--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="C12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="13">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.14</v>
+        <v>3.25</v>
       </c>
       <c r="C13" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="14">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D14" t="n">
-        <v>6.17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="C15" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="D15" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="16">

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
         <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="7">
@@ -535,10 +535,10 @@
         <v>4.2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="8">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="D9" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -608,71 +608,47 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5.25</v>
-      </c>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.91</v>
-      </c>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5</v>
-      </c>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.38</v>
-      </c>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -682,7 +658,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -692,7 +668,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -702,7 +678,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -712,7 +688,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -722,7 +698,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -732,222 +708,588 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.33</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="C28" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="D28" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="C29" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
         <v>3.2</v>
       </c>
       <c r="D30" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="C31" t="n">
         <v>3.4</v>
       </c>
       <c r="D31" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="C32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="D32" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.75</v>
+        <v>1.29</v>
       </c>
       <c r="C33" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>Aeu0r0Mk</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="C34" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D34" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>42SH31wI</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.2</v>
+        <v>1.44</v>
       </c>
       <c r="C35" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="C36" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="D36" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
           <t>IXMN9zkI</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B47" t="n">
         <v>2.55</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C47" t="n">
         <v>3.1</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D47" t="n">
         <v>2.75</v>
       </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,155 +608,215 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.45</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>Aeu0r0Mk</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="C24" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>42SH31wI</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -766,530 +826,210 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="C26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="D26" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>02s0k9od</t>
+          <t>8KIdPmPc</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="C27" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>8KfYbJz0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="C28" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>EL1P0u6m</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>M5TEBdK5</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C30" t="n">
         <v>3.2</v>
       </c>
       <c r="D30" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>joLV7EJU</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="C31" t="n">
         <v>3.4</v>
       </c>
       <c r="D31" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>WvwvCQVo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="C32" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="D32" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.29</v>
+        <v>2.75</v>
       </c>
       <c r="C33" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="D33" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>x0nkeyzP</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="C34" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="D34" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.44</v>
+        <v>3.2</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="C36" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="D36" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.33</v>
+        <v>2.55</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EL1P0u6m</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D39" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>M5TEBdK5</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D40" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>joLV7EJU</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D41" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>WvwvCQVo</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>tYhtcc5C</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D44" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>SORbFvLt</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>lvG7DIkg</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>IXMN9zkI</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C47" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
           <t>4CX22Dbk</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>CjGqFjre</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>0IkylEqd</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>CEhO9e6F</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>CxyB0iT1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>CSXdOfL8</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>ptW4MYkL</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>4QCyHCDr</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>hCxNBHy3</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>KvdW7ZzS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>Y54hDUC7</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>v3ivyY4E</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>W0WITkcl</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>YPSZP7dD</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>EL5MmBlK</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>tWk1tTtf</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>Eql9v7B6</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,98 +608,62 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="C13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15</v>
-      </c>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D14" t="n">
-        <v>8.5</v>
-      </c>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>8</v>
-      </c>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4.5</v>
-      </c>
+          <t>M7MVoOR0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>02s0k9od</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6</v>
-      </c>
+          <t>dbt7KrYP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -708,13 +672,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="C18" t="n">
         <v>4.1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="19">
@@ -743,7 +707,7 @@
         <v>2.88</v>
       </c>
       <c r="C20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="D20" t="n">
         <v>2.45</v>
@@ -836,13 +800,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="C26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D26" t="n">
         <v>3.2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="27">
@@ -868,7 +832,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="C28" t="n">
         <v>3.2</v>
@@ -1030,6 +994,76 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,167 +448,167 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3</v>
+        <v>1.33</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.25</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D4" t="n">
         <v>1.73</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
         <v>2.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9</v>
+        <v>1.44</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.95</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1</v>
+        <v>1.53</v>
       </c>
       <c r="C10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.85</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D11" t="n">
-        <v>9.5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -618,17 +618,23 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -638,7 +644,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -648,7 +654,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -658,7 +664,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -668,327 +674,207 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5.75</v>
-      </c>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="C19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>13</v>
-      </c>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2.45</v>
-      </c>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4.1</v>
-      </c>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.3</v>
-      </c>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>8.5</v>
-      </c>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4.75</v>
-      </c>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>8.5</v>
-      </c>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3.2</v>
-      </c>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="C27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>7.5</v>
-      </c>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.55</v>
-      </c>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D29" t="n">
-        <v>4.1</v>
-      </c>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2.75</v>
-      </c>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4.2</v>
-      </c>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2.75</v>
-      </c>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.5</v>
-      </c>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D34" t="n">
-        <v>4.33</v>
-      </c>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2.2</v>
-      </c>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2.75</v>
-      </c>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2.75</v>
-      </c>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>EL5MmBlK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -998,7 +884,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>tWk1tTtf</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1008,7 +894,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1018,7 +904,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1028,7 +914,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1038,7 +924,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1048,7 +934,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>ptW4MYkL</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1058,12 +944,92 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Ofy73Ced</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>CGH1PgIF</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,547 +448,547 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="D4" t="n">
-        <v>5.25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.95</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="C9" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.33</v>
+        <v>5.25</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D11" t="n">
-        <v>9.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.09</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.71</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.42</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.75</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.57</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="C18" t="n">
-        <v>4.1</v>
+        <v>4.56</v>
       </c>
       <c r="D18" t="n">
-        <v>5.75</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.17</v>
+        <v>2.15</v>
       </c>
       <c r="C19" t="n">
-        <v>7.5</v>
+        <v>3.44</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.88</v>
+        <v>1.94</v>
       </c>
       <c r="C20" t="n">
-        <v>3.25</v>
+        <v>3.69</v>
       </c>
       <c r="D20" t="n">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="C21" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="D21" t="n">
-        <v>4.1</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D22" t="n">
         <v>3</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>CjGqFjre</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="C23" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="D23" t="n">
-        <v>8.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>0IkylEqd</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="C24" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="D24" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D25" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>CxyB0iT1</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2.35</v>
       </c>
       <c r="C26" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D26" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>CSXdOfL8</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="C27" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="D27" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>ptW4MYkL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="C28" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>4QCyHCDr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="C29" t="n">
         <v>3.25</v>
       </c>
       <c r="D29" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>hCxNBHy3</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="C30" t="n">
         <v>3.2</v>
       </c>
       <c r="D30" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="C31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D31" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2.75</v>
-      </c>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.5</v>
-      </c>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D34" t="n">
-        <v>4.33</v>
-      </c>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="C35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2.2</v>
-      </c>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2.75</v>
-      </c>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2.75</v>
-      </c>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -998,7 +998,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1018,7 +1018,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1028,7 +1028,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1038,7 +1038,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>ptW4MYkL</t>
+          <t>Ofy73Ced</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1058,12 +1058,72 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>CGH1PgIF</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         <v>4.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="4">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="C4" t="n">
         <v>5.75</v>
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="C6" t="n">
         <v>4.75</v>
       </c>
       <c r="D6" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D7" t="n">
         <v>2.45</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D8" t="n">
         <v>6.5</v>
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="C10" t="n">
         <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="C11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="12">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="C12" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="D12" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="13">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="C13" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="D13" t="n">
-        <v>4.71</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="14">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="C14" t="n">
-        <v>4.08</v>
+        <v>3.8</v>
       </c>
       <c r="D14" t="n">
-        <v>6.42</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="15">
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="C15" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="D15" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -676,13 +676,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="C16" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="D16" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="17">
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="C17" t="n">
-        <v>4.66</v>
+        <v>4.33</v>
       </c>
       <c r="D17" t="n">
-        <v>6.57</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="18">
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="C18" t="n">
-        <v>4.56</v>
+        <v>4.33</v>
       </c>
       <c r="D18" t="n">
-        <v>6.78</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="19">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="C19" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="20">
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="C20" t="n">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="D20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="21">
@@ -756,374 +756,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="C21" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>4CX22Dbk</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>CjGqFjre</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>0IkylEqd</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>CEhO9e6F</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D25" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CxyB0iT1</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="C26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>CSXdOfL8</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>ptW4MYkL</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>4QCyHCDr</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>hCxNBHy3</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D30" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>KvdW7ZzS</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Y54hDUC7</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>v3ivyY4E</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>W0WITkcl</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>YPSZP7dD</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>EL5MmBlK</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>tWk1tTtf</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Eql9v7B6</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>zVpmZBZQ</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>SSPRRTR0</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>p4dhrkCs</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>v3JgRFm3</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>dtLQNtsB</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Ofy73Ced</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>CGH1PgIF</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>21OYHBAk</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>v5l07LdU</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>fHO9ROsn</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>jqIIP2Cb</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>GUXb5YQq</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>WIX2NXnS</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="3">
@@ -471,7 +471,7 @@
         <v>3.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D3" t="n">
         <v>2.35</v>
@@ -487,7 +487,7 @@
         <v>1.2</v>
       </c>
       <c r="C4" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
@@ -500,269 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>M7MVoOR0</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>dbt7KrYP</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>UilLdutJ</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2uc40Ntf</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>0hYMmpcl</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>fZZxp2dD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EaryFQkA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>WdSjHeFt</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>ELeQ0zVa</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>d4DGBiqI</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0xK7DDE5</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SjzlgqTj</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,65 +448,257 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>1.42</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="D2" t="n">
-        <v>1.67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="C4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D4" t="n">
         <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="C5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C15" t="n">
         <v>3.1</v>
       </c>
-      <c r="D5" t="n">
-        <v>2.88</v>
+      <c r="D15" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="C14" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="D14" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="15">

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,256 +448,192 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.45</v>
+        <v>3.6</v>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
         <v>3.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="C9" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="D9" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="D10" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="C11" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="C12" t="n">
         <v>3.4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="C13" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D17" t="n">
         <v>4.1</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,193 +448,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="C2" t="n">
         <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D3" t="n">
         <v>4.75</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C4" t="n">
         <v>3.6</v>
       </c>
-      <c r="C4" t="n">
-        <v>3.4</v>
-      </c>
       <c r="D4" t="n">
-        <v>1.95</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>5.75</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="C7" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="D9" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="C10" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D11" t="n">
         <v>3.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,110 +448,110 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="C3" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="D5" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="C8" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -560,49 +560,17 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,129 +448,65 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="C2" t="n">
         <v>3.75</v>
       </c>
       <c r="D2" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="C5" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,65 +448,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>n7VN5MCd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="C2" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>v1I9TP43</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="C2" t="n">
         <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         <v>4.5</v>
       </c>
       <c r="C3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="C4" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="C5" t="n">
         <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +522,7 @@
         <v>3.4</v>
       </c>
       <c r="D6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -603,6 +603,166 @@
       </c>
       <c r="D11" t="n">
         <v>5.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,321 +448,113 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>n7VN5MCd</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>v1I9TP43</t>
+          <t>zFWqD4KM</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D3" t="n">
         <v>4.5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SQjcKLRk</t>
+          <t>4WHcOkpL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="C4" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>8.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>6cNF7rrp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="D5" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>Esk5Iad2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>WIJkQBF8</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="C7" t="n">
         <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>rgFQPs4S</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2ucWYubt</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>44gmVcc5</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>S66wtFBN</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Yqo4RFdU</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>O8QDoJsn</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>A50vXJSh</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pOEMqcCb</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>WvDUsysB</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>xIieTySH</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,113 +448,321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>2ucWYubt</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="C2" t="n">
         <v>3.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>44gmVcc5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="C5" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="C6" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="D8" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>5.75</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,321 +448,129 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2ucWYubt</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>44gmVcc5</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="C3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D3" t="n">
         <v>3.4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>S66wtFBN</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Yqo4RFdU</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>O8QDoJsn</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>A50vXJSh</t>
+          <t>WvDUsysB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="D7" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pOEMqcCb</t>
+          <t>xIieTySH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WvDUsysB</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="C9" t="n">
         <v>4.5</v>
       </c>
       <c r="D9" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xIieTySH</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="C17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D20" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,113 +448,337 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="D2" t="n">
-        <v>2.25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="C5" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="C8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C19" t="n">
         <v>3.75</v>
       </c>
-      <c r="D8" t="n">
-        <v>5.75</v>
+      <c r="D19" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.45</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,330 +455,10 @@
         <v>1.48</v>
       </c>
       <c r="C2" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="D2" t="n">
         <v>6.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8SWavWAa</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>EB8yv2aJ</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ttV7xAuC</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>x8OGzlAO</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dzYLoEIP</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SW3Qfiet</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>lnhZhVPh</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SIOithtm</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.45</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,337 +448,145 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="C2" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="D2" t="n">
-        <v>6.25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="D3" t="n">
-        <v>7.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="C6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="C7" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="C8" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D9" t="n">
         <v>2.2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3</v>
+        <v>1.36</v>
       </c>
       <c r="C10" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8SWavWAa</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>EB8yv2aJ</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ttV7xAuC</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>x8OGzlAO</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dzYLoEIP</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SW3Qfiet</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>lnhZhVPh</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SIOithtm</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.45</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,145 +448,97 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.33</v>
+        <v>2.9</v>
       </c>
       <c r="C2" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="C3" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1.48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="C5" t="n">
         <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.55</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="C7" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C8" t="n">
         <v>3.4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,97 +448,193 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="D2" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>WUqjkmPH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4</v>
+        <v>1.45</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C11" t="n">
         <v>3.6</v>
       </c>
-      <c r="D7" t="n">
-        <v>3.4</v>
+      <c r="D11" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,193 +448,225 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.45</v>
+        <v>4.1</v>
       </c>
       <c r="C5" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
-        <v>6.5</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="n">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.91</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="C11" t="n">
         <v>3.6</v>
       </c>
       <c r="D11" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="D12" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="C13" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,226 +448,352 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="D7" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9</v>
+        <v>5.25</v>
       </c>
       <c r="C8" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="C9" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="D9" t="n">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>4.75</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="C11" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.57</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8</v>
+        <v>1.36</v>
       </c>
       <c r="C14" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="C15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C20" t="n">
         <v>3.5</v>
       </c>
-      <c r="D15" t="n">
-        <v>1.83</v>
-      </c>
+      <c r="D20" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +522,7 @@
         <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="7">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="C9" t="n">
         <v>3.1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="C10" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="D10" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="11">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="C13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D13" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14">
@@ -714,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="19">
@@ -794,6 +794,56 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="C4" t="n">
         <v>4.5</v>
@@ -506,7 +506,7 @@
         <v>3.25</v>
       </c>
       <c r="D5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="C6" t="n">
         <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="7">
@@ -586,7 +586,7 @@
         <v>3.75</v>
       </c>
       <c r="D10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="12">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="C12" t="n">
         <v>3.4</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="C13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -844,6 +844,26 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,422 +448,98 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.91</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.4</v>
+        <v>5.75</v>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="C5" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
-        <v>3.25</v>
-      </c>
       <c r="D7" t="n">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>dGwq9oAD</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>GMBD7YY8</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>0lpzB7u1</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>McP0d8Q7</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>I5fXHFho</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>bLD0NyVN</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>UuMqRJVb</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D14" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8f71RSPs</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OMVUWl2K</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D16" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>jeAhPc0B</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>OjcQLOgJ</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xY3xTu1n</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>jwaINpP6</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C20" t="n">
         <v>3.5</v>
       </c>
-      <c r="D20" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>fB59P6ff</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Ug79dz7j</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4CLi9Djd</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>WIDwXGr3</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>IFm4IHT9</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>0b5fTYsS</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Y96v2dqT</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>rcXrBZLq</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>EssDGebM</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Sp7nVfDF</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>p2kdKwac</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,98 +448,422 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.75</v>
+        <v>1.3</v>
       </c>
       <c r="C4" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.57</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="C6" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="D7" t="n">
         <v>3.5</v>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -490,380 +490,104 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8f71RSPs</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6</v>
+        <v>1.38</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="D5" t="n">
-        <v>2.05</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="C6" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>OjcQLOgJ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="C7" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="D7" t="n">
-        <v>3.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>xY3xTu1n</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="C8" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="D8" t="n">
-        <v>6.25</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>jwaINpP6</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="C9" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>fB59P6ff</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="C10" t="n">
         <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>fB59P6ff</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Ug79dz7j</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4CLi9Djd</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>WIDwXGr3</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IFm4IHT9</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0b5fTYsS</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Y96v2dqT</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D17" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>rcXrBZLq</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>EssDGebM</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Sp7nVfDF</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>p2kdKwac</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
         <v>2.8</v>
       </c>
-      <c r="C21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>rJ8JNC5k</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>pOryx3Qa</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Gpn0zjke</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>CCu9YTJ7</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>b7pTwPem</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>WvkEqfS8</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>v5hMsYdL</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>jqCRLjz2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>vJXfdXBE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>rXmhxCKr</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,146 +448,422 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="C3" t="n">
         <v>3.1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>IFm4IHT9</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.38</v>
+        <v>7.5</v>
       </c>
       <c r="C5" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>0b5fTYsS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>Y96v2dqT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="C7" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="D7" t="n">
-        <v>6.25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>rcXrBZLq</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="C8" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="D8" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>EssDGebM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.75</v>
+        <v>4.2</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>Sp7nVfDF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="C10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C12" t="n">
         <v>3.4</v>
       </c>
-      <c r="D10" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>bR8Aj2ug</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>E3zhYKPO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>S60RnKvI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>tjxpzseC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>pbap3uPb</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>hU52hOAt</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>KtcJltA5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,422 +448,162 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Ug79dz7j</t>
+          <t>rJ8JNC5k</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="C2" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.35</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4CLi9Djd</t>
+          <t>pOryx3Qa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WIDwXGr3</t>
+          <t>Gpn0zjke</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IFm4IHT9</t>
+          <t>CCu9YTJ7</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="C5" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.44</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0b5fTYsS</t>
+          <t>b7pTwPem</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="C6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D6" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Y96v2dqT</t>
+          <t>WvkEqfS8</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.3</v>
+        <v>4.75</v>
       </c>
       <c r="C7" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rcXrBZLq</t>
+          <t>v5hMsYdL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>7.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EssDGebM</t>
+          <t>jqCRLjz2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="C9" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sp7nVfDF</t>
+          <t>vJXfdXBE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>p2kdKwac</t>
+          <t>rXmhxCKr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="C11" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="D11" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rJ8JNC5k</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pOryx3Qa</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Gpn0zjke</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>CCu9YTJ7</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>b7pTwPem</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WvkEqfS8</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>v5hMsYdL</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="C18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>jqCRLjz2</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>vJXfdXBE</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>rXmhxCKr</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>bR8Aj2ug</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>OYgzob9U</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>hO2h1JgB</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>E3zhYKPO</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>S60RnKvI</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>tjxpzseC</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>pbap3uPb</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>hU52hOAt</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>voUq51fn</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>KtcJltA5</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -448,161 +448,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="C3" t="n">
         <v>3.25</v>
       </c>
       <c r="D3" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5</v>
+        <v>2.55</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C7" t="n">
         <v>4.75</v>
       </c>
-      <c r="C7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="D7" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.18</v>
+        <v>2.05</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.85</v>
+        <v>4.1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="n">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="C11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/italy/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,161 +448,177 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="C3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1.65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="C6" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="C7" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="D8" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.44</v>
+        <v>4.1</v>
       </c>
       <c r="C9" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D10" t="n">
         <v>4.1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.83</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="D11" t="n">
-        <v>4.2</v>
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z7KrCz8T</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
